--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -27908,12 +27908,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27947,81 +27947,100 @@
         </is>
       </c>
       <c r="N167" t="n">
+        <v>94</v>
+      </c>
+      <c r="O167" t="n">
+        <v>94</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.8784187602586344</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
         <v>2</v>
       </c>
-      <c r="O167" t="n">
-        <v>2</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
-      <c r="AT167" t="n">
-        <v>0</v>
-      </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28048,17 +28067,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28083,7 +28102,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -28092,81 +28111,175 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN168" t="b">
+        <v>1</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28341,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28373,7 +28486,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -28518,7 +28631,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -28527,13 +28640,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O171" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R171" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -28663,7 +28776,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -28808,7 +28921,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -28817,13 +28930,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O173" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R173" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -28953,7 +29066,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29098,7 +29211,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29107,13 +29220,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R175" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29213,12 +29326,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29243,12 +29356,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N176" t="n">
@@ -29291,42 +29404,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29358,12 +29471,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29388,109 +29501,90 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29517,17 +29611,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -29566,170 +29660,76 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN178" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP178" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AT178" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV178" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29761,12 +29761,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -29800,81 +29800,100 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29901,17 +29920,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -29945,22 +29964,39 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -29968,6 +30004,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>1</v>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -29980,7 +30074,7 @@
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
@@ -29990,7 +30084,7 @@
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT180" t="n">
@@ -29998,47 +30092,47 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30065,217 +30159,526 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>D123</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Tularemia</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
         <is>
           <t>土拉菌病</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="K183" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="inlineStr">
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
+      <c r="V183" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
-      <c r="W181" t="inlineStr">
+      <c r="W183" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X181" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>Tularemi</t>
         </is>
       </c>
-      <c r="Y181" t="inlineStr">
+      <c r="Y183" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
+      <c r="Z183" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA181" t="inlineStr">
+      <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB181" t="inlineStr">
+      <c r="AB183" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC181" t="inlineStr">
+      <c r="AC183" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD181" t="inlineStr">
+      <c r="AD183" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE181" t="inlineStr">
+      <c r="AE183" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF181" t="inlineStr">
+      <c r="AF183" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG181" t="inlineStr">
+      <c r="AG183" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH181" t="inlineStr">
+      <c r="AH183" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI181" t="inlineStr">
+      <c r="AI183" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ181" t="inlineStr">
+      <c r="AJ183" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK181" t="inlineStr">
+      <c r="AK183" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM181" t="inlineStr">
+      <c r="AM183" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN181" t="b">
+      <c r="AN183" t="b">
         <v>1</v>
       </c>
-      <c r="AO181" t="inlineStr">
+      <c r="AO183" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP181" t="inlineStr">
+      <c r="AP183" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ181" t="inlineStr">
+      <c r="AQ183" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR181" t="inlineStr">
+      <c r="AR183" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS181" t="inlineStr">
+      <c r="AS183" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
-      <c r="AT181" t="n">
+      <c r="AT183" t="n">
         <v>2</v>
       </c>
-      <c r="AU181" t="inlineStr">
+      <c r="AU183" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV181" t="inlineStr">
+      <c r="AV183" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW181" t="inlineStr">
+      <c r="AW183" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX181" t="inlineStr">
+      <c r="AX183" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY181" t="inlineStr">
+      <c r="AY183" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ181" t="inlineStr">
+      <c r="AZ183" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA181" t="inlineStr">
+      <c r="BA183" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB181" t="inlineStr">
+      <c r="BB183" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC181" t="inlineStr">
+      <c r="BC183" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -30397,7 +30800,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -30407,7 +30810,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -30427,7 +30830,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -30459,7 +30862,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>281</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -29616,12 +29616,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -29646,12 +29646,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N178" t="n">
@@ -29694,42 +29694,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29761,12 +29761,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -29800,100 +29800,81 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29901,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -29969,98 +29950,23 @@
       <c r="O180" t="n">
         <v>1</v>
       </c>
+      <c r="R180" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN180" t="b">
-        <v>1</v>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
@@ -30159,17 +30065,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30203,81 +30109,175 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN181" t="b">
+        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30309,12 +30309,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30361,87 +30361,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30449,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -30517,98 +30498,23 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -30679,6 +30585,245 @@
         </is>
       </c>
       <c r="BC183" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -30800,7 +30945,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -30810,7 +30955,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -26996,13 +26996,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O162" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R162" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27160,10 +27160,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O163" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -27544,13 +27544,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O165" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R165" t="n">
-        <v>0.4599337147068316</v>
+        <v>0.4953132312227418</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -27708,10 +27708,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O166" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -30493,13 +30493,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>0.2122770990954608</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -30657,10 +30657,10 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>376</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -26996,13 +26996,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R162" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27160,10 +27160,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O163" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -29945,13 +29945,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R180" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -30109,10 +30109,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -30826,6 +30826,151 @@
       <c r="BC184" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>1</v>
+      </c>
+      <c r="O185" t="n">
+        <v>1</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30862,7 +31007,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -30945,7 +31090,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -30955,7 +31100,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -31007,7 +31152,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -22872,12 +22872,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22911,81 +22911,92 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>18</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0.1998268611263263</v>
+        <v>0</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23012,17 +23023,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23056,22 +23067,39 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>4</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.07115236683456549</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1540</t>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -23079,6 +23107,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary tularemia notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23086,70 +23172,65 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1540</t>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23176,17 +23257,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23220,175 +23301,81 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O138" t="n">
-        <v>4</v>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.1998268611263263</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -23420,12 +23407,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23459,81 +23446,100 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23560,17 +23566,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23604,22 +23610,39 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O140" t="n">
-        <v>11</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0.1945873408375057</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -23627,6 +23650,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23639,7 +23720,7 @@
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
@@ -23649,7 +23730,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -23657,47 +23738,47 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23724,17 +23805,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23768,175 +23849,81 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>11</v>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23968,12 +23955,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24007,13 +23994,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="O142" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="R142" t="n">
-        <v>0.4111747388444672</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24022,7 +24009,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -24052,7 +24039,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -24065,42 +24052,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24132,12 +24119,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24171,29 +24158,29 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="O143" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>Harpest</t>
+          <t>Tularemi</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -24218,7 +24205,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -24253,17 +24240,17 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -24291,7 +24278,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -24304,42 +24291,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24358,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24401,7 +24388,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24410,81 +24397,100 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>0.4111747388444672</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR144" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24511,17 +24517,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24546,7 +24552,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -24555,81 +24561,175 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="O145" t="n">
-        <v>3</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24691,7 +24791,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -24836,7 +24936,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -24845,13 +24945,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24981,7 +25081,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25126,7 +25226,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25271,7 +25371,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25416,7 +25516,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25425,13 +25525,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25561,7 +25661,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25676,12 +25776,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -25706,12 +25806,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N153" t="n">
@@ -25754,42 +25854,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25821,12 +25921,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -25851,12 +25951,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N154" t="n">
@@ -25865,9 +25965,12 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -25896,42 +25999,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25963,12 +26066,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26007,9 +26110,12 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -26043,12 +26149,12 @@
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -26063,12 +26169,12 @@
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
@@ -26105,12 +26211,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26185,7 +26291,7 @@
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -26205,7 +26311,7 @@
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
@@ -26247,12 +26353,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26327,7 +26433,7 @@
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
@@ -26347,7 +26453,7 @@
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
@@ -26389,12 +26495,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26469,7 +26575,7 @@
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
@@ -26489,7 +26595,7 @@
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
@@ -26531,12 +26637,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26611,7 +26717,7 @@
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
@@ -26631,7 +26737,7 @@
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
@@ -26673,12 +26779,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -26753,7 +26859,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -26773,7 +26879,7 @@
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
@@ -26815,12 +26921,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -26895,7 +27001,7 @@
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
@@ -26915,7 +27021,7 @@
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
@@ -26957,12 +27063,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -26996,100 +27102,78 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>13</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0.2312451922123379</v>
+        <v>0</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27116,17 +27200,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27160,175 +27244,78 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>13</v>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AT163" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV163" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27360,12 +27347,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27399,81 +27386,100 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O164" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27500,17 +27506,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -27544,22 +27550,39 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O165" t="n">
-        <v>28</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0.4953132312227418</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -27567,6 +27590,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27579,7 +27660,7 @@
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
@@ -27589,7 +27670,7 @@
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT165" t="n">
@@ -27597,47 +27678,47 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27664,17 +27745,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -27708,175 +27789,81 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>28</v>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27908,12 +27895,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27947,13 +27934,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="O167" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="R167" t="n">
-        <v>0.8784187602586344</v>
+        <v>0.4953132312227418</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -27962,7 +27949,7 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -27992,7 +27979,7 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT167" t="n">
@@ -28005,42 +27992,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28072,12 +28059,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28111,29 +28098,29 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="O168" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>Harpest</t>
+          <t>Tularemi</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
@@ -28158,7 +28145,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -28193,17 +28180,17 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -28231,7 +28218,7 @@
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT168" t="n">
@@ -28244,42 +28231,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28311,12 +28298,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28350,81 +28337,100 @@
         </is>
       </c>
       <c r="N169" t="n">
+        <v>94</v>
+      </c>
+      <c r="O169" t="n">
+        <v>94</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.8784187602586344</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
         <v>2</v>
       </c>
-      <c r="O169" t="n">
-        <v>2</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP169" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
-      <c r="AT169" t="n">
-        <v>0</v>
-      </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28451,17 +28457,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -28486,7 +28492,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -28495,81 +28501,175 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28631,7 +28731,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -28776,7 +28876,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -28921,7 +29021,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -28930,13 +29030,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O173" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R173" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -29066,7 +29166,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29211,7 +29311,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29220,13 +29320,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O175" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R175" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29356,7 +29456,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29501,7 +29601,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29510,13 +29610,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R177" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -29646,7 +29746,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -29761,12 +29861,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -29791,22 +29891,22 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -29839,42 +29939,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29906,12 +30006,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -29936,109 +30036,90 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30065,17 +30146,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30109,175 +30190,81 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>2</v>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP181" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AT181" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV181" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30309,12 +30296,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30348,81 +30335,100 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30449,17 +30455,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -30493,22 +30499,39 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O183" t="n">
-        <v>12</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0.2122770990954608</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -30516,6 +30539,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
+        <v>1</v>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -30528,7 +30609,7 @@
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
@@ -30538,7 +30619,7 @@
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT183" t="n">
@@ -30546,47 +30627,47 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30613,17 +30694,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -30657,175 +30738,81 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
-        <v>12</v>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN184" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -30857,118 +30844,521 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>12</v>
+      </c>
+      <c r="O185" t="n">
+        <v>12</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.2122770990954608</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>12</v>
+      </c>
+      <c r="O186" t="n">
+        <v>12</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>D123</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Tularemia</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
         <is>
           <t>土拉菌病</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="K187" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N185" t="n">
+      <c r="N187" t="n">
         <v>1</v>
       </c>
-      <c r="O185" t="n">
+      <c r="O187" t="n">
         <v>1</v>
       </c>
-      <c r="R185" t="n">
+      <c r="R187" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S185" t="inlineStr">
+      <c r="S187" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO185" t="inlineStr">
+      <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP185" t="inlineStr">
+      <c r="AP187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR185" t="inlineStr">
+      <c r="AR187" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS185" t="inlineStr"/>
-      <c r="AT185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
+      <c r="AS187" t="inlineStr"/>
+      <c r="AT187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU187" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV185" t="inlineStr">
+      <c r="AV187" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW185" t="inlineStr">
+      <c r="AW187" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX185" t="inlineStr">
+      <c r="AX187" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY185" t="inlineStr">
+      <c r="AY187" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ185" t="inlineStr">
+      <c r="AZ187" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA185" t="inlineStr">
+      <c r="BA187" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB185" t="inlineStr">
+      <c r="BB187" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC185" t="inlineStr">
+      <c r="BC187" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -31090,7 +31480,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -31100,7 +31490,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -31120,7 +31510,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -30335,13 +30335,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O182" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R182" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -30499,10 +30499,10 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O183" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
@@ -31361,6 +31361,151 @@
       <c r="BC187" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr"/>
+      <c r="AT188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31397,7 +31542,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -31480,7 +31625,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -31490,7 +31635,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -31542,7 +31687,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -18971,13 +18971,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O111" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R111" t="n">
-        <v>0.2331313379807141</v>
+        <v>0.2442328302655099</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -23301,13 +23301,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O138" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R138" t="n">
-        <v>0.1998268611263263</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -27347,12 +27347,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27386,100 +27386,81 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O164" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R164" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.08881193827836725</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -27506,7 +27487,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -27555,98 +27536,23 @@
       <c r="O165" t="n">
         <v>13</v>
       </c>
+      <c r="R165" t="n">
+        <v>0.2312451922123379</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U165" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
@@ -27745,17 +27651,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -27789,81 +27695,175 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27895,12 +27895,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27934,100 +27934,81 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>0.4953132312227418</v>
+        <v>0</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28054,7 +28035,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -28103,98 +28084,23 @@
       <c r="O168" t="n">
         <v>28</v>
       </c>
+      <c r="R168" t="n">
+        <v>0.4953132312227418</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN168" t="b">
-        <v>1</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -28293,17 +28199,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28337,22 +28243,39 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="O169" t="n">
-        <v>94</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0.8784187602586344</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -28360,6 +28283,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -28382,7 +28363,7 @@
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT169" t="n">
@@ -28395,42 +28376,42 @@
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28438,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -28506,98 +28487,23 @@
       <c r="O170" t="n">
         <v>94</v>
       </c>
+      <c r="R170" t="n">
+        <v>0.8784187602586344</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>Harpest</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN170" t="b">
-        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
@@ -28696,17 +28602,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -28740,81 +28646,175 @@
         </is>
       </c>
       <c r="N171" t="n">
+        <v>94</v>
+      </c>
+      <c r="O171" t="n">
+        <v>94</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
         <v>2</v>
       </c>
-      <c r="O171" t="n">
-        <v>2</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP171" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
-      <c r="AT171" t="n">
-        <v>0</v>
-      </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28846,12 +28846,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -28876,7 +28876,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -28885,13 +28885,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -28924,42 +28924,42 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28991,12 +28991,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29021,7 +29021,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -29030,13 +29030,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -29069,42 +29069,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29136,12 +29136,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29175,13 +29175,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -29214,42 +29214,42 @@
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29281,12 +29281,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29311,7 +29311,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29320,13 +29320,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>0.001432519066384693</v>
+        <v>0</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29359,42 +29359,42 @@
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29426,12 +29426,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29456,7 +29456,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29465,13 +29465,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O176" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29504,42 +29504,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29571,12 +29571,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29601,7 +29601,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29610,13 +29610,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -29649,42 +29649,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29716,12 +29716,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -29746,7 +29746,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -29755,13 +29755,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -29794,42 +29794,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29861,12 +29861,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -29891,7 +29891,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -29900,13 +29900,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -29939,42 +29939,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30006,12 +30006,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -30036,7 +30036,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -30045,13 +30045,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -30084,42 +30084,42 @@
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30151,12 +30151,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30181,12 +30181,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N181" t="n">
@@ -30229,42 +30229,42 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30296,12 +30296,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30335,100 +30335,81 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>0.08894045854320688</v>
+        <v>0</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30455,7 +30436,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -30504,98 +30485,23 @@
       <c r="O183" t="n">
         <v>5</v>
       </c>
+      <c r="R183" t="n">
+        <v>0.08894045854320688</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -30694,17 +30600,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -30738,81 +30644,175 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30844,12 +30844,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -30883,100 +30883,81 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>0.2122770990954608</v>
+        <v>0</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31003,7 +30984,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -31047,103 +31028,28 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O186" t="n">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0.4245541981909216</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U186" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -31242,17 +31148,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -31277,7 +31183,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -31286,81 +31192,175 @@
         </is>
       </c>
       <c r="N187" t="n">
+        <v>24</v>
+      </c>
+      <c r="O187" t="n">
+        <v>24</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
         <v>1</v>
       </c>
-      <c r="O187" t="n">
-        <v>1</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -31392,12 +31392,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -31431,13 +31431,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -31470,40 +31470,185 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
+      <c r="AT189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW188" t="inlineStr">
+      <c r="AW189" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX188" t="inlineStr">
+      <c r="AX189" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY188" t="inlineStr">
+      <c r="AY189" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ188" t="inlineStr">
+      <c r="AZ189" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA188" t="inlineStr">
+      <c r="BA189" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB188" t="inlineStr">
+      <c r="BB189" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC188" t="inlineStr">
+      <c r="BC189" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -31625,7 +31770,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
@@ -31635,7 +31780,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -31687,7 +31832,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>398</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -24397,13 +24397,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O144" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R144" t="n">
-        <v>0.4111747388444672</v>
+        <v>0.4018298584161838</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24561,10 +24561,10 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O145" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -28482,13 +28482,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O170" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R170" t="n">
-        <v>0.8784187602586344</v>
+        <v>0.8690738798303511</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -28646,10 +28646,10 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O171" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
@@ -30480,13 +30480,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O183" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R183" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -30644,10 +30644,10 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O184" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -31028,13 +31028,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="O186" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="R186" t="n">
-        <v>0.4245541981909216</v>
+        <v>0.583762022512517</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -31192,10 +31192,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="O187" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -31651,6 +31651,296 @@
       <c r="BC189" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
+      <c r="AT190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" t="n">
+        <v>1</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
+      <c r="AT191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31687,7 +31977,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -31770,7 +32060,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -31780,7 +32070,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11">
@@ -31832,7 +32122,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>424</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -28482,13 +28482,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O170" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R170" t="n">
-        <v>0.8690738798303511</v>
+        <v>0.8597289994020678</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -28646,10 +28646,10 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O171" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
@@ -30480,13 +30480,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O183" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R183" t="n">
-        <v>0.142304733669131</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -30644,10 +30644,10 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O184" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -31941,6 +31941,844 @@
       <c r="BC191" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="n">
+        <v>1</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
+      <c r="AT193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AT194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AT195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31977,7 +32815,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -32060,7 +32898,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
@@ -32070,7 +32908,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -32090,7 +32928,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -32122,7 +32960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24250,7 +24250,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28335,7 +28335,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -30480,13 +30480,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O183" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R183" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -30644,10 +30644,10 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O184" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -31028,13 +31028,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="O186" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="R186" t="n">
-        <v>0.583762022512517</v>
+        <v>0.7606596050920676</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -31192,10 +31192,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="O187" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -32301,13 +32301,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -32465,10 +32465,10 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>440</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2471,6 +2516,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3019,6 +3069,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3407,7 +3462,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -3973,6 +4028,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4269,6 +4329,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4565,6 +4630,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4861,6 +4931,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5157,6 +5232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5305,6 +5385,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5450,6 +5535,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5595,6 +5685,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5740,6 +5835,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5885,6 +5985,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6030,6 +6135,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6175,6 +6285,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6320,6 +6435,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6465,6 +6585,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7000,6 +7125,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7548,6 +7678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7936,7 +8071,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -8650,6 +8785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8946,6 +9086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9242,6 +9387,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9538,6 +9688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9686,6 +9841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9831,6 +9991,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9976,6 +10141,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10121,6 +10291,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10266,6 +10441,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10411,6 +10591,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10556,6 +10741,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10701,6 +10891,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10846,6 +11041,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11381,6 +11581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11929,6 +12134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12317,7 +12527,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -13031,6 +13241,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13327,6 +13542,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13623,6 +13843,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13919,6 +14144,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14064,6 +14294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14209,6 +14444,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14354,6 +14594,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14499,6 +14744,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14644,6 +14894,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14789,6 +15044,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14934,6 +15194,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15079,6 +15344,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15224,6 +15494,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15759,6 +16034,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16307,6 +16587,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16695,7 +16980,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -17409,6 +17694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17705,6 +17995,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18001,6 +18296,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18297,6 +18597,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18442,6 +18747,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18587,6 +18897,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18732,6 +19047,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18877,6 +19197,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19022,6 +19347,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19167,6 +19497,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19312,6 +19647,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19457,6 +19797,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19602,6 +19947,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20137,6 +20487,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20685,6 +21040,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21073,7 +21433,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -21787,6 +22147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22083,6 +22448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22379,6 +22749,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22675,6 +23050,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22968,6 +23348,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23113,6 +23498,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23258,6 +23648,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23403,6 +23798,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23548,6 +23948,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23693,6 +24098,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23838,6 +24248,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23983,6 +24398,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24128,6 +24548,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24273,6 +24698,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24808,6 +25238,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25356,6 +25791,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25744,7 +26184,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -26452,6 +26892,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26742,6 +27187,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27032,6 +27482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27322,6 +27777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27467,6 +27927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27612,6 +28077,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27757,6 +28227,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27902,6 +28377,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28047,6 +28527,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28192,6 +28677,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28337,6 +28827,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28482,6 +28977,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28627,6 +29127,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29162,6 +29667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29710,6 +30220,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30098,7 +30613,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -30806,6 +31321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31096,6 +31616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31386,6 +31911,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31676,6 +32206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31966,6 +32501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32111,6 +32651,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32256,6 +32801,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32401,6 +32951,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32546,6 +33101,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32691,6 +33251,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32836,6 +33401,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32981,6 +33551,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33126,6 +33701,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33219,12 +33799,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -33258,81 +33838,92 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
-        <v>8</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.08881193827836725</v>
+        <v>0</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -33359,17 +33950,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -33403,22 +33994,39 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
-        <v>13</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0.2312451922123379</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1540</t>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -33426,6 +34034,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary tularemia notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33433,70 +34099,65 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1540</t>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -33523,17 +34184,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -33567,39 +34228,17 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O206" t="n">
-        <v>13</v>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>8</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.08881193827836725</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -33607,135 +34246,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
-      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -33767,12 +34339,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -33806,81 +34378,100 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33907,17 +34498,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -33951,22 +34542,39 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O208" t="n">
-        <v>28</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0.4953132312227418</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -33974,6 +34582,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33986,7 +34652,7 @@
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
@@ -33996,7 +34662,7 @@
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT208" t="n">
@@ -34004,47 +34670,47 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34071,17 +34737,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -34115,39 +34781,17 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>28</v>
-      </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -34155,135 +34799,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
-      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34315,12 +34892,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -34354,13 +34931,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="O210" t="n">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="R210" t="n">
-        <v>0.8597289994020678</v>
+        <v>0.4953132312227418</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -34369,7 +34946,7 @@
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -34399,7 +34976,7 @@
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT210" t="n">
@@ -34412,42 +34989,42 @@
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34479,12 +35056,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -34518,29 +35095,29 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="O211" t="n">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>Harpest</t>
+          <t>Tularemi</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
@@ -34565,7 +35142,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -34600,17 +35177,17 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -34638,7 +35215,7 @@
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
@@ -34651,42 +35228,42 @@
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34718,12 +35295,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -34757,81 +35334,100 @@
         </is>
       </c>
       <c r="N212" t="n">
+        <v>91</v>
+      </c>
+      <c r="O212" t="n">
+        <v>91</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.8503841189737845</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
         <v>2</v>
       </c>
-      <c r="O212" t="n">
-        <v>2</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP212" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
-      <c r="AT212" t="n">
-        <v>0</v>
-      </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34858,17 +35454,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -34893,7 +35489,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -34902,81 +35498,175 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>91</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR213" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35038,7 +35728,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -35058,6 +35748,11 @@
       <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -35183,7 +35878,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -35328,7 +36023,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -35337,17 +36032,22 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O216" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R216" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -35473,7 +36173,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -35618,7 +36318,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -35627,17 +36327,22 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O218" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R218" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -35763,7 +36468,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -35908,7 +36613,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -35917,17 +36622,22 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R220" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -36053,7 +36763,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -36168,12 +36878,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -36198,26 +36908,31 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -36246,42 +36961,42 @@
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36313,12 +37028,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -36343,12 +37058,12 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N223" t="n">
@@ -36362,7 +37077,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -36391,42 +37106,42 @@
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36458,12 +37173,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -36507,7 +37222,12 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -36541,12 +37261,12 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -36561,12 +37281,12 @@
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
@@ -36603,12 +37323,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -36653,6 +37373,11 @@
       <c r="S225" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -36686,7 +37411,7 @@
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
@@ -36706,7 +37431,7 @@
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
@@ -36748,12 +37473,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -36798,6 +37523,11 @@
       <c r="S226" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -36831,7 +37561,7 @@
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
@@ -36851,7 +37581,7 @@
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
@@ -36893,12 +37623,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -36943,6 +37673,11 @@
       <c r="S227" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -36976,7 +37711,7 @@
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
@@ -36996,7 +37731,7 @@
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
@@ -37038,12 +37773,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -37088,6 +37823,11 @@
       <c r="S228" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -37121,7 +37861,7 @@
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
@@ -37141,7 +37881,7 @@
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
@@ -37183,12 +37923,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -37233,6 +37973,11 @@
       <c r="S229" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -37266,7 +38011,7 @@
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
@@ -37286,7 +38031,7 @@
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
@@ -37328,12 +38073,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -37378,6 +38123,11 @@
       <c r="S230" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -37411,7 +38161,7 @@
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
@@ -37431,7 +38181,7 @@
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
@@ -37473,12 +38223,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -37512,22 +38262,17 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>0.2490332839209793</v>
+        <v>0</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -37537,75 +38282,66 @@
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37632,17 +38368,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -37676,39 +38412,17 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
-        <v>14</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -37716,135 +38430,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
+      <c r="AT232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO232" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP232" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AT232" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV232" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37876,12 +38523,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -37915,81 +38562,100 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38016,17 +38682,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -38060,22 +38726,39 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="O234" t="n">
-        <v>43</v>
-      </c>
-      <c r="R234" t="n">
-        <v>0.7606596050920676</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>14</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -38083,6 +38766,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38095,7 +38836,7 @@
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
@@ -38105,7 +38846,7 @@
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT234" t="n">
@@ -38113,47 +38854,47 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38180,17 +38921,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -38224,39 +38965,17 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>43</v>
-      </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -38264,135 +38983,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
-        <v>1</v>
-      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38424,12 +39076,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -38454,7 +39106,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -38463,81 +39115,100 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="O236" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="R236" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.9552469459295734</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38564,17 +39235,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -38599,7 +39270,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -38608,81 +39279,175 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O237" t="n">
-        <v>0</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0</v>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN237" t="b">
+        <v>1</v>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38714,12 +39479,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -38744,7 +39509,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -38753,81 +39518,100 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>1.270903738246535</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -38854,17 +39638,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -38889,7 +39673,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -38898,81 +39682,175 @@
         </is>
       </c>
       <c r="N239" t="n">
+        <v>136</v>
+      </c>
+      <c r="O239" t="n">
+        <v>136</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
         <v>1</v>
       </c>
-      <c r="O239" t="n">
-        <v>1</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39004,12 +39882,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -39034,7 +39912,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -39043,17 +39921,22 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -39082,42 +39965,42 @@
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39149,12 +40032,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -39179,7 +40062,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -39188,13 +40071,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -39227,42 +40110,42 @@
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39324,7 +40207,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -39439,12 +40322,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -39469,12 +40352,12 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N243" t="n">
@@ -39484,94 +40367,80 @@
         <v>1</v>
       </c>
       <c r="R243" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39598,17 +40467,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -39633,184 +40502,90 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39842,12 +40617,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -39872,26 +40647,31 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO245" t="inlineStr">
@@ -39920,42 +40700,1143 @@
       </c>
       <c r="AV245" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>1</v>
+      </c>
+      <c r="O247" t="n">
+        <v>1</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AT247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>1</v>
+      </c>
+      <c r="O248" t="n">
+        <v>1</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AT248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA248" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
+      <c r="AT249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV249" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW245" t="inlineStr">
+      <c r="AW249" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX245" t="inlineStr">
+      <c r="AX249" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY245" t="inlineStr">
+      <c r="AY249" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ245" t="inlineStr">
+      <c r="AZ249" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA245" t="inlineStr">
+      <c r="BA249" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB245" t="inlineStr">
+      <c r="BB249" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC245" t="inlineStr">
+      <c r="BC249" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>4</v>
+      </c>
+      <c r="O250" t="n">
+        <v>4</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>4</v>
+      </c>
+      <c r="O251" t="n">
+        <v>4</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40075,7 +41956,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -40085,7 +41966,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -40105,7 +41986,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -40137,7 +42018,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>452</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -40951,13 +40951,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O247" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R247" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -41115,10 +41115,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O248" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -39115,13 +39115,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O236" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R236" t="n">
-        <v>0.9552469459295734</v>
+        <v>0.9729367041875284</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -39279,10 +39279,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O237" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U237" t="inlineStr">
         <is>
@@ -39518,13 +39518,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O238" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R238" t="n">
-        <v>1.270903738246535</v>
+        <v>1.252213977389968</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -39682,10 +39682,10 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O239" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
@@ -41504,13 +41504,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O250" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R250" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.2299668573534158</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -41668,10 +41668,10 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O251" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
@@ -41837,6 +41837,151 @@
       <c r="BC251" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
+      <c r="AT252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41873,7 +42018,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -41956,7 +42101,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -41966,7 +42111,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -42018,7 +42163,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -8774,9 +8774,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -13832,9 +13829,6 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -17127,13 +17121,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R101" t="n">
-        <v>0.07475904342626677</v>
+        <v>0.06541416299798342</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -17291,10 +17285,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -17683,9 +17677,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -22136,9 +22127,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -22437,9 +22425,6 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -30760,13 +30745,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O184" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R184" t="n">
-        <v>0.4018298584161838</v>
+        <v>0.3924849779879006</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -30924,10 +30909,10 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O185" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
@@ -42163,7 +42148,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16">
